--- a/update/historicos/expectativas_inflacion_peru.xlsx
+++ b/update/historicos/expectativas_inflacion_peru.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2800,6 +2800,14 @@
         <v>3.05</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B298" t="n">
+        <v>3.0875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
